--- a/results/scenario_base_case/rp_weights.xlsx
+++ b/results/scenario_base_case/rp_weights.xlsx
@@ -442,7 +442,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>89</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4">
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
@@ -502,17 +502,17 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>rp08</t>
+          <t>rp_design</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
